--- a/ValueSet-promis-global-skala-5-vs.xlsx
+++ b/ValueSet-promis-global-skala-5-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
